--- a/assets/xlsx/일별투자수익_2026-08-21_2026-08-27.xlsx
+++ b/assets/xlsx/일별투자수익_2026-08-21_2026-08-27.xlsx
@@ -19,7 +19,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -32,11 +32,6 @@
       <b val="1"/>
       <color rgb="00111827"/>
       <sz val="13"/>
-    </font>
-    <font>
-      <name val="맑은 고딕"/>
-      <color rgb="009CA3AF"/>
-      <sz val="9"/>
     </font>
     <font>
       <name val="맑은 고딕"/>
@@ -100,21 +95,20 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="10" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="5" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="10" fontId="5" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="4" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="4" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -480,7 +474,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.5" customWidth="1" min="1" max="1"/>
@@ -498,226 +492,212 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>※ 예시값 — 표기 금액·요율·상호는 전부 예시이며 실제 거래 기록이 아니다. 수수료율은 미확정이고 할인율 0.11%는 예정값이다.</t>
-        </is>
-      </c>
-    </row>
     <row r="3" ht="24" customHeight="1">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>정산예정일</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>상환액</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>투자실행금</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>투자 수익</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>W금융일수</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>Ty수익율</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>2026-08-21</t>
         </is>
       </c>
-      <c r="B4" s="5" t="n">
+      <c r="B4" s="4" t="n">
         <v>179096790</v>
       </c>
-      <c r="C4" s="5" t="n">
+      <c r="C4" s="4" t="n">
         <v>178900000</v>
       </c>
-      <c r="D4" s="5" t="n">
+      <c r="D4" s="4" t="n">
         <v>196790</v>
       </c>
-      <c r="E4" s="6" t="n">
-        <v>11.4</v>
-      </c>
-      <c r="F4" s="7" t="n">
-        <v>0.0352</v>
+      <c r="E4" s="5" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="F4" s="6" t="n">
+        <v>0.1384</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>2026-08-22</t>
         </is>
       </c>
-      <c r="B5" s="5" t="n">
+      <c r="B5" s="4" t="n">
         <v>172789860</v>
       </c>
-      <c r="C5" s="5" t="n">
+      <c r="C5" s="4" t="n">
         <v>172600000</v>
       </c>
-      <c r="D5" s="5" t="n">
+      <c r="D5" s="4" t="n">
         <v>189860</v>
       </c>
-      <c r="E5" s="6" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="F5" s="7" t="n">
-        <v>0.0362</v>
+      <c r="E5" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="F5" s="6" t="n">
+        <v>0.1338</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="3" t="inlineStr">
         <is>
           <t>2026-08-23</t>
         </is>
       </c>
-      <c r="B6" s="5" t="n">
+      <c r="B6" s="4" t="n">
         <v>165481830</v>
       </c>
-      <c r="C6" s="5" t="n">
+      <c r="C6" s="4" t="n">
         <v>165300000</v>
       </c>
-      <c r="D6" s="5" t="n">
+      <c r="D6" s="4" t="n">
         <v>181830</v>
       </c>
-      <c r="E6" s="6" t="n">
-        <v>10.9</v>
-      </c>
-      <c r="F6" s="7" t="n">
-        <v>0.0368</v>
+      <c r="E6" s="5" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="F6" s="6" t="n">
+        <v>0.1255</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="3" t="inlineStr">
         <is>
           <t>2026-08-24</t>
         </is>
       </c>
-      <c r="B7" s="5" t="n">
+      <c r="B7" s="4" t="n">
         <v>187906470</v>
       </c>
-      <c r="C7" s="5" t="n">
+      <c r="C7" s="4" t="n">
         <v>187700000</v>
       </c>
-      <c r="D7" s="5" t="n">
+      <c r="D7" s="4" t="n">
         <v>206470</v>
       </c>
-      <c r="E7" s="6" t="n">
-        <v>11.6</v>
-      </c>
-      <c r="F7" s="7" t="n">
-        <v>0.0346</v>
+      <c r="E7" s="5" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>0.1217</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="A8" s="3" t="inlineStr">
         <is>
           <t>2026-08-25</t>
         </is>
       </c>
-      <c r="B8" s="5" t="n">
+      <c r="B8" s="4" t="n">
         <v>183301410</v>
       </c>
-      <c r="C8" s="5" t="n">
+      <c r="C8" s="4" t="n">
         <v>183100000</v>
       </c>
-      <c r="D8" s="5" t="n">
+      <c r="D8" s="4" t="n">
         <v>201410</v>
       </c>
-      <c r="E8" s="6" t="n">
-        <v>11.3</v>
-      </c>
-      <c r="F8" s="7" t="n">
-        <v>0.0355</v>
+      <c r="E8" s="5" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="F8" s="6" t="n">
+        <v>0.1295</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="3" t="inlineStr">
         <is>
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="B9" s="5" t="n">
+      <c r="B9" s="4" t="n">
         <v>176794260</v>
       </c>
-      <c r="C9" s="5" t="n">
+      <c r="C9" s="4" t="n">
         <v>176600000</v>
       </c>
-      <c r="D9" s="5" t="n">
+      <c r="D9" s="4" t="n">
         <v>194260</v>
       </c>
-      <c r="E9" s="6" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="F9" s="7" t="n">
-        <v>0.0358</v>
+      <c r="E9" s="5" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="F9" s="6" t="n">
+        <v>0.1255</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="inlineStr">
+      <c r="A10" s="3" t="inlineStr">
         <is>
           <t>2026-08-27</t>
         </is>
       </c>
-      <c r="B10" s="5" t="n">
+      <c r="B10" s="4" t="n">
         <v>186805260</v>
       </c>
-      <c r="C10" s="5" t="n">
+      <c r="C10" s="4" t="n">
         <v>186600000</v>
       </c>
-      <c r="D10" s="5" t="n">
+      <c r="D10" s="4" t="n">
         <v>205260</v>
       </c>
-      <c r="E10" s="6" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="F10" s="7" t="n">
-        <v>0.0349</v>
+      <c r="E10" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="F10" s="6" t="n">
+        <v>0.1338</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="8" t="inlineStr">
+      <c r="A11" s="7" t="inlineStr">
         <is>
           <t>합계</t>
         </is>
       </c>
-      <c r="B11" s="9" t="n">
+      <c r="B11" s="8" t="n">
         <v>1252175880</v>
       </c>
-      <c r="C11" s="9" t="n">
+      <c r="C11" s="8" t="n">
         <v>1250800000</v>
       </c>
-      <c r="D11" s="9" t="n">
+      <c r="D11" s="8" t="n">
         <v>1375880</v>
       </c>
-      <c r="E11" s="10" t="n">
-        <v>11.3</v>
-      </c>
-      <c r="F11" s="11" t="n">
-        <v>0.0355</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>※ 합계행의 W금융일수·Ty수익율은 투자금액 가중평균(단순평균 아님) — 11.3일 / 3.55%.</t>
-        </is>
+      <c r="E11" s="9" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="F11" s="10" t="n">
+        <v>0.1295</v>
       </c>
     </row>
   </sheetData>
